--- a/current-excel-manifests/FileAnnotationTemplate.xlsx
+++ b/current-excel-manifests/FileAnnotationTemplate.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="561">
   <si>
     <t>Component</t>
   </si>
@@ -984,628 +984,631 @@
     <t>json</t>
   </si>
   <si>
+    <t>Emory_Levey_300_CSF_FNIH</t>
+  </si>
+  <si>
+    <t>transcript quantification</t>
+  </si>
+  <si>
+    <t>label free mass spectrometry</t>
+  </si>
+  <si>
+    <t>locs</t>
+  </si>
+  <si>
     <t>EmoryDrosophilaTau</t>
   </si>
   <si>
-    <t>transcript quantification</t>
-  </si>
-  <si>
-    <t>label free mass spectrometry</t>
-  </si>
-  <si>
-    <t>locs</t>
+    <t>variancePartition</t>
+  </si>
+  <si>
+    <t>Laser Speckle Imaging</t>
+  </si>
+  <si>
+    <t>maf</t>
   </si>
   <si>
     <t>EpiGABA</t>
   </si>
   <si>
-    <t>variancePartition</t>
-  </si>
-  <si>
-    <t>Laser Speckle Imaging</t>
-  </si>
-  <si>
-    <t>maf</t>
+    <t>Variant calling</t>
+  </si>
+  <si>
+    <t>LC-MS</t>
+  </si>
+  <si>
+    <t>mat</t>
   </si>
   <si>
     <t>EpiMap</t>
   </si>
   <si>
-    <t>Variant calling</t>
-  </si>
-  <si>
-    <t>LC-MS</t>
-  </si>
-  <si>
-    <t>mat</t>
+    <t>visualization</t>
+  </si>
+  <si>
+    <t>LC-MSMS</t>
+  </si>
+  <si>
+    <t>md</t>
   </si>
   <si>
     <t>eQTLmetaAnalysis</t>
   </si>
   <si>
-    <t>visualization</t>
-  </si>
-  <si>
-    <t>LC-MSMS</t>
-  </si>
-  <si>
-    <t>md</t>
+    <t>LC-SRM</t>
+  </si>
+  <si>
+    <t>mov</t>
   </si>
   <si>
     <t>FreshMicro</t>
   </si>
   <si>
-    <t>LC-SRM</t>
-  </si>
-  <si>
-    <t>mov</t>
+    <t>Leiden Oxylipins</t>
+  </si>
+  <si>
+    <t>mp4</t>
   </si>
   <si>
     <t>HBI_scRNAseq</t>
   </si>
   <si>
-    <t>Leiden Oxylipins</t>
-  </si>
-  <si>
-    <t>mp4</t>
+    <t>lentiMPRA</t>
+  </si>
+  <si>
+    <t>msf</t>
   </si>
   <si>
     <t>HBTRC</t>
   </si>
   <si>
-    <t>lentiMPRA</t>
-  </si>
-  <si>
-    <t>msf</t>
+    <t>LFP</t>
+  </si>
+  <si>
+    <t>mtx</t>
   </si>
   <si>
     <t>HDAC1-cKOBrain</t>
   </si>
   <si>
-    <t>LFP</t>
-  </si>
-  <si>
-    <t>mtx</t>
+    <t>liquid chromatography-electrochemical detection</t>
+  </si>
+  <si>
+    <t>nirs</t>
   </si>
   <si>
     <t>HumanFC</t>
   </si>
   <si>
-    <t>liquid chromatography-electrochemical detection</t>
-  </si>
-  <si>
-    <t>nirs</t>
+    <t>lncrnaSeq</t>
+  </si>
+  <si>
+    <t>pdf</t>
   </si>
   <si>
     <t>IL10_APPmouse</t>
   </si>
   <si>
-    <t>lncrnaSeq</t>
-  </si>
-  <si>
-    <t>pdf</t>
+    <t>locomotor activation behavior</t>
+  </si>
+  <si>
+    <t>pdresult</t>
   </si>
   <si>
     <t>iNiAstshRNA</t>
   </si>
   <si>
-    <t>locomotor activation behavior</t>
-  </si>
-  <si>
-    <t>pdresult</t>
+    <t>long-read rnaSeq</t>
+  </si>
+  <si>
+    <t>pdstudy</t>
   </si>
   <si>
     <t>IntegrativePathwayAnalysis</t>
   </si>
   <si>
-    <t>long-read rnaSeq</t>
-  </si>
-  <si>
-    <t>pdstudy</t>
+    <t>LTP</t>
+  </si>
+  <si>
+    <t>pdview</t>
   </si>
   <si>
     <t>iPSC</t>
   </si>
   <si>
-    <t>LTP</t>
-  </si>
-  <si>
-    <t>pdview</t>
+    <t>m6A-rnaSeq</t>
+  </si>
+  <si>
+    <t>plink</t>
   </si>
   <si>
     <t>iPSC-HiC</t>
   </si>
   <si>
-    <t>m6A-rnaSeq</t>
-  </si>
-  <si>
-    <t>plink</t>
+    <t>MDMS-SL</t>
+  </si>
+  <si>
+    <t>png</t>
   </si>
   <si>
     <t>iPSCAstrocytes</t>
   </si>
   <si>
-    <t>MDMS-SL</t>
-  </si>
-  <si>
-    <t>png</t>
+    <t>memory behavior</t>
+  </si>
+  <si>
+    <t>powerpoint</t>
   </si>
   <si>
     <t>iPSCMicroglia</t>
   </si>
   <si>
-    <t>memory behavior</t>
-  </si>
-  <si>
-    <t>powerpoint</t>
+    <t>Metabolon</t>
+  </si>
+  <si>
+    <t>Python script</t>
   </si>
   <si>
     <t>ISB_Taner_CollagenDomain</t>
   </si>
   <si>
-    <t>Metabolon</t>
-  </si>
-  <si>
-    <t>Python script</t>
+    <t>methylationArray</t>
+  </si>
+  <si>
+    <t>pzfx</t>
   </si>
   <si>
     <t>ISB_Taner_Cxcl10</t>
   </si>
   <si>
-    <t>methylationArray</t>
-  </si>
-  <si>
-    <t>pzfx</t>
+    <t>MIB/MS</t>
+  </si>
+  <si>
+    <t>R script</t>
   </si>
   <si>
     <t>ISB_Taner_PTN_MDK</t>
   </si>
   <si>
-    <t>MIB/MS</t>
-  </si>
-  <si>
-    <t>R script</t>
+    <t>microRNAcounts</t>
   </si>
   <si>
     <t>ISB_Taner_sIL10r_sIL4r</t>
   </si>
   <si>
-    <t>microRNAcounts</t>
+    <t>mirnaArray</t>
+  </si>
+  <si>
+    <t>RCC</t>
   </si>
   <si>
     <t>ISB_Taner_TGFbeta</t>
   </si>
   <si>
-    <t>mirnaArray</t>
-  </si>
-  <si>
-    <t>RCC</t>
+    <t>mirnaSeq</t>
+  </si>
+  <si>
+    <t>RData</t>
   </si>
   <si>
     <t>Jax.IU.Pitt.Proteomics_Metabolomics_Pilot</t>
   </si>
   <si>
-    <t>mirnaSeq</t>
-  </si>
-  <si>
-    <t>RData</t>
+    <t>MRI</t>
+  </si>
+  <si>
+    <t>recal</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_APOE4.Trem2.R47H</t>
   </si>
   <si>
-    <t>MRI</t>
-  </si>
-  <si>
-    <t>recal</t>
+    <t>mRNAcounts</t>
+  </si>
+  <si>
+    <t>RLF</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_APP.PS1</t>
   </si>
   <si>
-    <t>mRNAcounts</t>
-  </si>
-  <si>
-    <t>RLF</t>
+    <t>mRNAseq</t>
+  </si>
+  <si>
+    <t>rmd</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_Levetiracetam-5XFAD</t>
   </si>
   <si>
-    <t>mRNAseq</t>
-  </si>
-  <si>
-    <t>rmd</t>
+    <t>MudPIT</t>
+  </si>
+  <si>
+    <t>saf</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_LOAD2.PrimaryScreen</t>
   </si>
   <si>
-    <t>MudPIT</t>
-  </si>
-  <si>
-    <t>saf</t>
+    <t>nextGenerationTargetedSequencing</t>
+  </si>
+  <si>
+    <t>sam</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_MicrobiomePilot</t>
   </si>
   <si>
-    <t>nextGenerationTargetedSequencing</t>
-  </si>
-  <si>
-    <t>sam</t>
+    <t>Nightingale NMR</t>
+  </si>
+  <si>
+    <t>sav</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_PrimaryScreen</t>
   </si>
   <si>
-    <t>Nightingale NMR</t>
-  </si>
-  <si>
-    <t>sav</t>
+    <t>NOMe-Seq</t>
+  </si>
+  <si>
+    <t>sdf</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_StrainValidation</t>
   </si>
   <si>
-    <t>NOMe-Seq</t>
-  </si>
-  <si>
-    <t>sdf</t>
+    <t>novelty response behavior</t>
+  </si>
+  <si>
+    <t>seg</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_Verubecestat_5XFAD</t>
   </si>
   <si>
-    <t>novelty response behavior</t>
-  </si>
-  <si>
-    <t>seg</t>
+    <t>open field test</t>
+  </si>
+  <si>
+    <t>Sentrix descriptor file</t>
   </si>
   <si>
     <t>LBP</t>
   </si>
   <si>
-    <t>open field test</t>
-  </si>
-  <si>
-    <t>Sentrix descriptor file</t>
+    <t>oxBS-Seq</t>
+  </si>
+  <si>
+    <t>sf3</t>
   </si>
   <si>
     <t>LillyMicroglia</t>
   </si>
   <si>
-    <t>oxBS-Seq</t>
-  </si>
-  <si>
-    <t>sf3</t>
+    <t>pharmacodynamics</t>
+  </si>
+  <si>
+    <t>sif</t>
   </si>
   <si>
     <t>LLFS</t>
   </si>
   <si>
-    <t>pharmacodynamics</t>
-  </si>
-  <si>
-    <t>sif</t>
+    <t>pharmacokinetics</t>
+  </si>
+  <si>
+    <t>sqlite</t>
   </si>
   <si>
     <t>lncRNA Pilot</t>
   </si>
   <si>
-    <t>pharmacokinetics</t>
-  </si>
-  <si>
-    <t>sqlite</t>
+    <t>photograph</t>
+  </si>
+  <si>
+    <t>sra</t>
   </si>
   <si>
     <t>MARS WISCONSIN</t>
   </si>
   <si>
-    <t>photograph</t>
-  </si>
-  <si>
-    <t>sra</t>
+    <t>polymeraseChainReaction</t>
+  </si>
+  <si>
+    <t>svg</t>
   </si>
   <si>
     <t>MayoeGWAS</t>
   </si>
   <si>
-    <t>polymeraseChainReaction</t>
-  </si>
-  <si>
-    <t>svg</t>
+    <t>Positron Emission Tomography</t>
+  </si>
+  <si>
+    <t>svs</t>
   </si>
   <si>
     <t>MayoHippocampus</t>
   </si>
   <si>
-    <t>Positron Emission Tomography</t>
-  </si>
-  <si>
-    <t>svs</t>
+    <t>proximity extension assay</t>
+  </si>
+  <si>
+    <t>Synapse Table</t>
   </si>
   <si>
     <t>MayoLOADGWAS</t>
   </si>
   <si>
-    <t>proximity extension assay</t>
-  </si>
-  <si>
-    <t>Synapse Table</t>
+    <t>questionnaire</t>
+  </si>
+  <si>
+    <t>tab</t>
   </si>
   <si>
     <t>MayoPilotRNAseq</t>
   </si>
   <si>
-    <t>questionnaire</t>
-  </si>
-  <si>
-    <t>tab</t>
+    <t>Rader Lipidomics</t>
+  </si>
+  <si>
+    <t>tagAlign</t>
   </si>
   <si>
     <t>MayoRNAseq</t>
   </si>
   <si>
-    <t>Rader Lipidomics</t>
-  </si>
-  <si>
-    <t>tagAlign</t>
+    <t>Real Time PCR</t>
+  </si>
+  <si>
+    <t>tar</t>
   </si>
   <si>
     <t>MC-BrAD</t>
   </si>
   <si>
-    <t>Real Time PCR</t>
-  </si>
-  <si>
-    <t>tar</t>
+    <t>Ribo-Seq</t>
+  </si>
+  <si>
+    <t>tbi</t>
   </si>
   <si>
     <t>MC-CAA</t>
   </si>
   <si>
-    <t>Ribo-Seq</t>
-  </si>
-  <si>
-    <t>tbi</t>
+    <t>rnaArray</t>
+  </si>
+  <si>
+    <t>tif</t>
   </si>
   <si>
     <t>MC_snRNA</t>
   </si>
   <si>
-    <t>rnaArray</t>
-  </si>
-  <si>
-    <t>tif</t>
+    <t>rnaSeq</t>
+  </si>
+  <si>
+    <t>tranches</t>
   </si>
   <si>
     <t>mCITE-Seq</t>
   </si>
   <si>
-    <t>rnaSeq</t>
-  </si>
-  <si>
-    <t>tranches</t>
+    <t>rotarod performance test</t>
+  </si>
+  <si>
+    <t>tsv</t>
   </si>
   <si>
     <t>MCMPS</t>
   </si>
   <si>
-    <t>rotarod performance test</t>
-  </si>
-  <si>
-    <t>tsv</t>
+    <t>RPPA</t>
+  </si>
+  <si>
+    <t>txt</t>
   </si>
   <si>
     <t>MEF2_Resilience</t>
   </si>
   <si>
-    <t>RPPA</t>
-  </si>
-  <si>
-    <t>txt</t>
+    <t>RRBS</t>
+  </si>
+  <si>
+    <t>vcf</t>
   </si>
   <si>
     <t>MindPhenomeKB</t>
   </si>
   <si>
-    <t>RRBS</t>
-  </si>
-  <si>
-    <t>vcf</t>
+    <t>sandwich ELISA</t>
+  </si>
+  <si>
+    <t>wiggle</t>
   </si>
   <si>
     <t>miR155</t>
   </si>
   <si>
-    <t>sandwich ELISA</t>
-  </si>
-  <si>
-    <t>wiggle</t>
+    <t>Sanger sequencing</t>
+  </si>
+  <si>
+    <t>xml</t>
   </si>
   <si>
     <t>MIT_ROSMAP_Multiomics</t>
   </si>
   <si>
-    <t>Sanger sequencing</t>
-  </si>
-  <si>
-    <t>xml</t>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>yaml</t>
   </si>
   <si>
     <t>MOA-PAD</t>
   </si>
   <si>
-    <t>scale</t>
-  </si>
-  <si>
-    <t>yaml</t>
+    <t>scATACSeq</t>
+  </si>
+  <si>
+    <t>zip</t>
   </si>
   <si>
     <t>MODEL-AD_5XFAD</t>
   </si>
   <si>
-    <t>scATACSeq</t>
-  </si>
-  <si>
-    <t>zip</t>
+    <t>scCGIseq</t>
   </si>
   <si>
     <t>MODEL-AD_Abca7_APOE4_Trem2</t>
   </si>
   <si>
-    <t>scCGIseq</t>
+    <t>scirnaSeq</t>
   </si>
   <si>
     <t>MODEL-AD_APOE4_KI</t>
   </si>
   <si>
-    <t>scirnaSeq</t>
+    <t>scrnaSeq</t>
   </si>
   <si>
     <t>MODEL-AD_APOE4_Trem2</t>
   </si>
   <si>
-    <t>scrnaSeq</t>
+    <t>scwholeGenomeSeq</t>
   </si>
   <si>
     <t>MODEL-AD_Ceacam_KO_APOE4_Trem2</t>
   </si>
   <si>
-    <t>scwholeGenomeSeq</t>
+    <t>SiMoA</t>
   </si>
   <si>
     <t>MODEL-AD_hAbeta_KI</t>
   </si>
   <si>
-    <t>SiMoA</t>
+    <t>snATACSeq</t>
   </si>
   <si>
     <t>MODEL-AD_Harmonization</t>
   </si>
   <si>
-    <t>snATACSeq</t>
+    <t>snpArray</t>
   </si>
   <si>
     <t>MODEL-AD_hCR1_KI_on_APOE4_Trem2</t>
   </si>
   <si>
-    <t>snpArray</t>
+    <t>snrnaSeq</t>
   </si>
   <si>
     <t>MODEL-AD_hTau_Trem2</t>
   </si>
   <si>
-    <t>snrnaSeq</t>
+    <t>spontaneous alternation</t>
   </si>
   <si>
     <t>MODEL-AD_Il1rapKO_APOE4_Trem2_exon2KO</t>
   </si>
   <si>
-    <t>spontaneous alternation</t>
+    <t>STARRSeq</t>
   </si>
   <si>
     <t>MODEL-AD_Mthfr_APOE4_Trem2</t>
   </si>
   <si>
-    <t>STARRSeq</t>
+    <t>TMT quantitation</t>
   </si>
   <si>
     <t>MODEL-AD_Rat_F344</t>
   </si>
   <si>
-    <t>TMT quantitation</t>
+    <t>TotalRNAseq</t>
   </si>
   <si>
     <t>MODEL-AD_Trem2_R47H</t>
   </si>
   <si>
-    <t>TotalRNAseq</t>
+    <t>tractionForceMicroscopy</t>
   </si>
   <si>
     <t>MouseHAL</t>
   </si>
   <si>
-    <t>tractionForceMicroscopy</t>
+    <t>UC Davis GCTOF</t>
   </si>
   <si>
     <t>MRGWAS</t>
   </si>
   <si>
-    <t>UC Davis GCTOF</t>
+    <t>UCSD Untargeted Metabolomics</t>
   </si>
   <si>
     <t>MSBB</t>
   </si>
   <si>
-    <t>UCSD Untargeted Metabolomics</t>
+    <t>UPLC-ESI-QTOF-MS</t>
   </si>
   <si>
     <t>MSBB_ArrayTissuePanel</t>
   </si>
   <si>
-    <t>UPLC-ESI-QTOF-MS</t>
+    <t>UPLC-MSMS</t>
   </si>
   <si>
     <t>MSDM</t>
   </si>
   <si>
-    <t>UPLC-MSMS</t>
+    <t>Vernier Caliper</t>
   </si>
   <si>
     <t>MSMM</t>
   </si>
   <si>
-    <t>Vernier Caliper</t>
+    <t>von Frey test</t>
   </si>
   <si>
     <t>MSSMiPSC</t>
   </si>
   <si>
-    <t>von Frey test</t>
+    <t>westernBlot</t>
   </si>
   <si>
     <t>mtDNA_AD</t>
   </si>
   <si>
-    <t>westernBlot</t>
+    <t>wheel running</t>
   </si>
   <si>
     <t>NAPS</t>
   </si>
   <si>
-    <t>wheel running</t>
+    <t>whole-cell patch clamp</t>
   </si>
   <si>
     <t>NHP-Chimpanzee</t>
   </si>
   <si>
-    <t>whole-cell patch clamp</t>
+    <t>wholeGenomeSeq</t>
   </si>
   <si>
     <t>NHP-Macaque</t>
   </si>
   <si>
-    <t>wholeGenomeSeq</t>
+    <t>Wishart Catecholamines</t>
   </si>
   <si>
     <t>NPS-AD</t>
   </si>
   <si>
-    <t>Wishart Catecholamines</t>
+    <t>Wishart High Value Metabolites</t>
   </si>
   <si>
     <t>OFMM</t>
   </si>
   <si>
-    <t>Wishart High Value Metabolites</t>
+    <t>Zeno Electronic Walkway</t>
   </si>
   <si>
     <t>omicsADDS</t>
-  </si>
-  <si>
-    <t>Zeno Electronic Walkway</t>
   </si>
   <si>
     <t>Organoid_scRNAseq</t>
@@ -29184,37 +29187,40 @@
       <formula>$M1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O1:O1000">
+    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+      <formula>$K1 = "analysis"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N1000">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+      <formula>$K1 = "metadata"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1000">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>$K1 = "experimentalData"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R1000">
+    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1000">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
-      <formula>$K1 = "experimentalData"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1000">
-    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1000">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N1000">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
-      <formula>$K1 = "metadata"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O1000">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
-      <formula>$K1 = "analysis"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
+      <formula1>Sheet2!$I$2:$I$185</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
       <formula1>Sheet2!$P$2:$P$3</formula1>
     </dataValidation>
@@ -29226,9 +29232,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="G2:G1000">
       <formula1>Sheet2!$G$2:$G$97</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
-      <formula1>Sheet2!$I$2:$I$184</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="Q2:Q1000">
       <formula1>Sheet2!$Q$2:$Q$26</formula1>
@@ -31327,6 +31330,11 @@
         <v>559</v>
       </c>
     </row>
+    <row r="185">
+      <c r="I185" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/current-excel-manifests/FileAnnotationTemplate.xlsx
+++ b/current-excel-manifests/FileAnnotationTemplate.xlsx
@@ -29209,23 +29209,23 @@
       <formula>$K1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1000">
-    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="M1:M1000">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>$K1 = "experimentalData"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:L1000">
+    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1000">
-    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1000">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
-      <formula>$K1 = "experimentalData"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1000">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+  <conditionalFormatting sqref="R1:R1000">
+    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/current-excel-manifests/FileAnnotationTemplate.xlsx
+++ b/current-excel-manifests/FileAnnotationTemplate.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="568">
   <si>
     <t>Component</t>
   </si>
@@ -984,630 +984,633 @@
     <t>json</t>
   </si>
   <si>
+    <t>DivCo_HS</t>
+  </si>
+  <si>
+    <t>transcript quantification</t>
+  </si>
+  <si>
+    <t>label free mass spectrometry</t>
+  </si>
+  <si>
+    <t>locs</t>
+  </si>
+  <si>
     <t>DukeAD_PTSD</t>
   </si>
   <si>
-    <t>transcript quantification</t>
-  </si>
-  <si>
-    <t>label free mass spectrometry</t>
-  </si>
-  <si>
-    <t>locs</t>
+    <t>variancePartition</t>
+  </si>
+  <si>
+    <t>Laser Speckle Imaging</t>
+  </si>
+  <si>
+    <t>maf</t>
   </si>
   <si>
     <t>ELPSCRNA</t>
   </si>
   <si>
-    <t>variancePartition</t>
-  </si>
-  <si>
-    <t>Laser Speckle Imaging</t>
-  </si>
-  <si>
-    <t>maf</t>
+    <t>Variant calling</t>
+  </si>
+  <si>
+    <t>LC-MS</t>
+  </si>
+  <si>
+    <t>mat</t>
   </si>
   <si>
     <t>Emory_ADRC</t>
   </si>
   <si>
-    <t>Variant calling</t>
-  </si>
-  <si>
-    <t>LC-MS</t>
-  </si>
-  <si>
-    <t>mat</t>
+    <t>visualization</t>
+  </si>
+  <si>
+    <t>LC-MSMS</t>
+  </si>
+  <si>
+    <t>md</t>
   </si>
   <si>
     <t>Emory_Levey_300_CSF_FNIH</t>
   </si>
   <si>
-    <t>visualization</t>
-  </si>
-  <si>
-    <t>LC-MSMS</t>
-  </si>
-  <si>
-    <t>md</t>
+    <t>LC-SRM</t>
+  </si>
+  <si>
+    <t>mov</t>
   </si>
   <si>
     <t>EmoryDrosophilaTau</t>
   </si>
   <si>
-    <t>LC-SRM</t>
-  </si>
-  <si>
-    <t>mov</t>
+    <t>Leiden Oxylipins</t>
+  </si>
+  <si>
+    <t>mp4</t>
   </si>
   <si>
     <t>EpiGABA</t>
   </si>
   <si>
-    <t>Leiden Oxylipins</t>
-  </si>
-  <si>
-    <t>mp4</t>
+    <t>lentiMPRA</t>
+  </si>
+  <si>
+    <t>msf</t>
   </si>
   <si>
     <t>EpiMap</t>
   </si>
   <si>
-    <t>lentiMPRA</t>
-  </si>
-  <si>
-    <t>msf</t>
+    <t>LFP</t>
+  </si>
+  <si>
+    <t>mtx</t>
   </si>
   <si>
     <t>eQTLmetaAnalysis</t>
   </si>
   <si>
-    <t>LFP</t>
-  </si>
-  <si>
-    <t>mtx</t>
+    <t>liquid chromatography-electrochemical detection</t>
+  </si>
+  <si>
+    <t>nirs</t>
   </si>
   <si>
     <t>FreshMicro</t>
   </si>
   <si>
-    <t>liquid chromatography-electrochemical detection</t>
-  </si>
-  <si>
-    <t>nirs</t>
+    <t>lncrnaSeq</t>
+  </si>
+  <si>
+    <t>pdf</t>
   </si>
   <si>
     <t>HBI_scRNAseq</t>
   </si>
   <si>
-    <t>lncrnaSeq</t>
-  </si>
-  <si>
-    <t>pdf</t>
+    <t>locomotor activation behavior</t>
+  </si>
+  <si>
+    <t>pdresult</t>
   </si>
   <si>
     <t>HBTRC</t>
   </si>
   <si>
-    <t>locomotor activation behavior</t>
-  </si>
-  <si>
-    <t>pdresult</t>
+    <t>long-read rnaSeq</t>
+  </si>
+  <si>
+    <t>pdstudy</t>
   </si>
   <si>
     <t>HDAC1-cKOBrain</t>
   </si>
   <si>
-    <t>long-read rnaSeq</t>
-  </si>
-  <si>
-    <t>pdstudy</t>
+    <t>LTP</t>
+  </si>
+  <si>
+    <t>pdview</t>
   </si>
   <si>
     <t>HumanFC</t>
   </si>
   <si>
-    <t>LTP</t>
-  </si>
-  <si>
-    <t>pdview</t>
+    <t>m6A-rnaSeq</t>
+  </si>
+  <si>
+    <t>plink</t>
   </si>
   <si>
     <t>IL10_APPmouse</t>
   </si>
   <si>
-    <t>m6A-rnaSeq</t>
-  </si>
-  <si>
-    <t>plink</t>
+    <t>MDMS-SL</t>
+  </si>
+  <si>
+    <t>png</t>
   </si>
   <si>
     <t>iNiAstshRNA</t>
   </si>
   <si>
-    <t>MDMS-SL</t>
-  </si>
-  <si>
-    <t>png</t>
+    <t>memory behavior</t>
+  </si>
+  <si>
+    <t>powerpoint</t>
   </si>
   <si>
     <t>IntegrativePathwayAnalysis</t>
   </si>
   <si>
-    <t>memory behavior</t>
-  </si>
-  <si>
-    <t>powerpoint</t>
+    <t>Metabolon</t>
+  </si>
+  <si>
+    <t>Python script</t>
   </si>
   <si>
     <t>iPSC</t>
   </si>
   <si>
-    <t>Metabolon</t>
-  </si>
-  <si>
-    <t>Python script</t>
+    <t>methylationArray</t>
+  </si>
+  <si>
+    <t>pzfx</t>
   </si>
   <si>
     <t>iPSC-HiC</t>
   </si>
   <si>
-    <t>methylationArray</t>
-  </si>
-  <si>
-    <t>pzfx</t>
+    <t>MIB/MS</t>
+  </si>
+  <si>
+    <t>R script</t>
   </si>
   <si>
     <t>iPSCAstrocytes</t>
   </si>
   <si>
-    <t>MIB/MS</t>
-  </si>
-  <si>
-    <t>R script</t>
+    <t>microRNAcounts</t>
   </si>
   <si>
     <t>iPSCMicroglia</t>
   </si>
   <si>
-    <t>microRNAcounts</t>
+    <t>mirnaArray</t>
+  </si>
+  <si>
+    <t>RCC</t>
   </si>
   <si>
     <t>ISB_Taner_CollagenDomain</t>
   </si>
   <si>
-    <t>mirnaArray</t>
-  </si>
-  <si>
-    <t>RCC</t>
+    <t>mirnaSeq</t>
+  </si>
+  <si>
+    <t>RData</t>
   </si>
   <si>
     <t>ISB_Taner_Cxcl10</t>
   </si>
   <si>
-    <t>mirnaSeq</t>
-  </si>
-  <si>
-    <t>RData</t>
+    <t>MRI</t>
+  </si>
+  <si>
+    <t>recal</t>
   </si>
   <si>
     <t>ISB_Taner_PTN_MDK</t>
   </si>
   <si>
-    <t>MRI</t>
-  </si>
-  <si>
-    <t>recal</t>
+    <t>mRNAcounts</t>
+  </si>
+  <si>
+    <t>RLF</t>
   </si>
   <si>
     <t>ISB_Taner_sIL10r_sIL4r</t>
   </si>
   <si>
-    <t>mRNAcounts</t>
-  </si>
-  <si>
-    <t>RLF</t>
+    <t>mRNAseq</t>
+  </si>
+  <si>
+    <t>rmd</t>
   </si>
   <si>
     <t>ISB_Taner_TGFbeta</t>
   </si>
   <si>
-    <t>mRNAseq</t>
-  </si>
-  <si>
-    <t>rmd</t>
+    <t>MudPIT</t>
+  </si>
+  <si>
+    <t>saf</t>
   </si>
   <si>
     <t>Jax.IU.Pitt.Proteomics_Metabolomics_Pilot</t>
   </si>
   <si>
-    <t>MudPIT</t>
-  </si>
-  <si>
-    <t>saf</t>
+    <t>nextGenerationTargetedSequencing</t>
+  </si>
+  <si>
+    <t>sam</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_APOE4.Trem2.R47H</t>
   </si>
   <si>
-    <t>nextGenerationTargetedSequencing</t>
-  </si>
-  <si>
-    <t>sam</t>
+    <t>Nightingale NMR</t>
+  </si>
+  <si>
+    <t>sav</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_APP.PS1</t>
   </si>
   <si>
-    <t>Nightingale NMR</t>
-  </si>
-  <si>
-    <t>sav</t>
+    <t>NOMe-Seq</t>
+  </si>
+  <si>
+    <t>sdf</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_Levetiracetam-5XFAD</t>
   </si>
   <si>
-    <t>NOMe-Seq</t>
-  </si>
-  <si>
-    <t>sdf</t>
+    <t>novelty response behavior</t>
+  </si>
+  <si>
+    <t>seg</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_LOAD2.PrimaryScreen</t>
   </si>
   <si>
-    <t>novelty response behavior</t>
-  </si>
-  <si>
-    <t>seg</t>
+    <t>open field test</t>
+  </si>
+  <si>
+    <t>Sentrix descriptor file</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_MicrobiomePilot</t>
   </si>
   <si>
-    <t>open field test</t>
-  </si>
-  <si>
-    <t>Sentrix descriptor file</t>
+    <t>oxBS-Seq</t>
+  </si>
+  <si>
+    <t>sf3</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_PrimaryScreen</t>
   </si>
   <si>
-    <t>oxBS-Seq</t>
-  </si>
-  <si>
-    <t>sf3</t>
+    <t>pharmacodynamics</t>
+  </si>
+  <si>
+    <t>sif</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_StrainValidation</t>
   </si>
   <si>
-    <t>pharmacodynamics</t>
-  </si>
-  <si>
-    <t>sif</t>
+    <t>pharmacokinetics</t>
+  </si>
+  <si>
+    <t>sqlite</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_Verubecestat_5XFAD</t>
   </si>
   <si>
-    <t>pharmacokinetics</t>
-  </si>
-  <si>
-    <t>sqlite</t>
+    <t>photograph</t>
+  </si>
+  <si>
+    <t>sra</t>
   </si>
   <si>
     <t>LBP</t>
   </si>
   <si>
-    <t>photograph</t>
-  </si>
-  <si>
-    <t>sra</t>
+    <t>polymeraseChainReaction</t>
+  </si>
+  <si>
+    <t>svg</t>
   </si>
   <si>
     <t>LillyMicroglia</t>
   </si>
   <si>
-    <t>polymeraseChainReaction</t>
-  </si>
-  <si>
-    <t>svg</t>
+    <t>Positron Emission Tomography</t>
+  </si>
+  <si>
+    <t>svs</t>
   </si>
   <si>
     <t>LLFS</t>
   </si>
   <si>
-    <t>Positron Emission Tomography</t>
-  </si>
-  <si>
-    <t>svs</t>
+    <t>proximity extension assay</t>
+  </si>
+  <si>
+    <t>Synapse Table</t>
   </si>
   <si>
     <t>lncRNA Pilot</t>
   </si>
   <si>
-    <t>proximity extension assay</t>
-  </si>
-  <si>
-    <t>Synapse Table</t>
+    <t>questionnaire</t>
+  </si>
+  <si>
+    <t>tab</t>
   </si>
   <si>
     <t>MARS WISCONSIN</t>
   </si>
   <si>
-    <t>questionnaire</t>
-  </si>
-  <si>
-    <t>tab</t>
+    <t>Rader Lipidomics</t>
+  </si>
+  <si>
+    <t>tagAlign</t>
   </si>
   <si>
     <t>MayoeGWAS</t>
   </si>
   <si>
-    <t>Rader Lipidomics</t>
-  </si>
-  <si>
-    <t>tagAlign</t>
+    <t>Real Time PCR</t>
+  </si>
+  <si>
+    <t>tar</t>
   </si>
   <si>
     <t>MayoHippocampus</t>
   </si>
   <si>
-    <t>Real Time PCR</t>
-  </si>
-  <si>
-    <t>tar</t>
+    <t>Ribo-Seq</t>
+  </si>
+  <si>
+    <t>tbi</t>
   </si>
   <si>
     <t>MayoLOADGWAS</t>
   </si>
   <si>
-    <t>Ribo-Seq</t>
-  </si>
-  <si>
-    <t>tbi</t>
+    <t>rnaArray</t>
+  </si>
+  <si>
+    <t>tif</t>
   </si>
   <si>
     <t>MayoPilotRNAseq</t>
   </si>
   <si>
-    <t>rnaArray</t>
-  </si>
-  <si>
-    <t>tif</t>
+    <t>rnaSeq</t>
+  </si>
+  <si>
+    <t>tranches</t>
   </si>
   <si>
     <t>MayoRNAseq</t>
   </si>
   <si>
-    <t>rnaSeq</t>
-  </si>
-  <si>
-    <t>tranches</t>
+    <t>rotarod performance test</t>
+  </si>
+  <si>
+    <t>tsv</t>
   </si>
   <si>
     <t>MC-BrAD</t>
   </si>
   <si>
-    <t>rotarod performance test</t>
-  </si>
-  <si>
-    <t>tsv</t>
+    <t>RPPA</t>
+  </si>
+  <si>
+    <t>txt</t>
   </si>
   <si>
     <t>MC-CAA</t>
   </si>
   <si>
-    <t>RPPA</t>
-  </si>
-  <si>
-    <t>txt</t>
+    <t>RRBS</t>
+  </si>
+  <si>
+    <t>vcf</t>
   </si>
   <si>
     <t>MC_snRNA</t>
   </si>
   <si>
-    <t>RRBS</t>
-  </si>
-  <si>
-    <t>vcf</t>
+    <t>sandwich ELISA</t>
+  </si>
+  <si>
+    <t>wiggle</t>
   </si>
   <si>
     <t>mCITE-Seq</t>
   </si>
   <si>
-    <t>sandwich ELISA</t>
-  </si>
-  <si>
-    <t>wiggle</t>
+    <t>Sanger sequencing</t>
+  </si>
+  <si>
+    <t>xml</t>
   </si>
   <si>
     <t>MCMPS</t>
   </si>
   <si>
-    <t>Sanger sequencing</t>
-  </si>
-  <si>
-    <t>xml</t>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>yaml</t>
   </si>
   <si>
     <t>MEF2_Resilience</t>
   </si>
   <si>
-    <t>scale</t>
-  </si>
-  <si>
-    <t>yaml</t>
+    <t>scATACSeq</t>
+  </si>
+  <si>
+    <t>zip</t>
   </si>
   <si>
     <t>MindPhenomeKB</t>
   </si>
   <si>
-    <t>scATACSeq</t>
-  </si>
-  <si>
-    <t>zip</t>
+    <t>scCGIseq</t>
   </si>
   <si>
     <t>miR155</t>
   </si>
   <si>
-    <t>scCGIseq</t>
+    <t>scirnaSeq</t>
   </si>
   <si>
     <t>MIT_ROSMAP_Multiomics</t>
   </si>
   <si>
-    <t>scirnaSeq</t>
+    <t>scrnaSeq</t>
   </si>
   <si>
     <t>MOA-PAD</t>
   </si>
   <si>
-    <t>scrnaSeq</t>
+    <t>scwholeGenomeSeq</t>
   </si>
   <si>
     <t>MODEL-AD_5XFAD</t>
   </si>
   <si>
-    <t>scwholeGenomeSeq</t>
+    <t>SiMoA</t>
   </si>
   <si>
     <t>MODEL-AD_Abca7_APOE4_Trem2</t>
   </si>
   <si>
-    <t>SiMoA</t>
+    <t>snATACSeq</t>
   </si>
   <si>
     <t>MODEL-AD_APOE4_KI</t>
   </si>
   <si>
-    <t>snATACSeq</t>
+    <t>snpArray</t>
   </si>
   <si>
     <t>MODEL-AD_APOE4_Trem2</t>
   </si>
   <si>
-    <t>snpArray</t>
+    <t>snrnaSeq</t>
   </si>
   <si>
     <t>MODEL-AD_Ceacam_KO_APOE4_Trem2</t>
   </si>
   <si>
-    <t>snrnaSeq</t>
+    <t>spontaneous alternation</t>
   </si>
   <si>
     <t>MODEL-AD_hAbeta_KI</t>
   </si>
   <si>
-    <t>spontaneous alternation</t>
+    <t>STARRSeq</t>
   </si>
   <si>
     <t>MODEL-AD_Harmonization</t>
   </si>
   <si>
-    <t>STARRSeq</t>
+    <t>TMT quantitation</t>
   </si>
   <si>
     <t>MODEL-AD_hCR1_KI_on_APOE4_Trem2</t>
   </si>
   <si>
-    <t>TMT quantitation</t>
+    <t>TotalRNAseq</t>
   </si>
   <si>
     <t>MODEL-AD_hTau_Trem2</t>
   </si>
   <si>
-    <t>TotalRNAseq</t>
+    <t>tractionForceMicroscopy</t>
   </si>
   <si>
     <t>MODEL-AD_Il1rapKO_APOE4_Trem2_exon2KO</t>
   </si>
   <si>
-    <t>tractionForceMicroscopy</t>
+    <t>UC Davis GCTOF</t>
   </si>
   <si>
     <t>MODEL-AD_Mthfr_APOE4_Trem2</t>
   </si>
   <si>
-    <t>UC Davis GCTOF</t>
+    <t>UCSD Untargeted Metabolomics</t>
   </si>
   <si>
     <t>MODEL-AD_Rat_F344</t>
   </si>
   <si>
-    <t>UCSD Untargeted Metabolomics</t>
+    <t>UPLC-ESI-QTOF-MS</t>
   </si>
   <si>
     <t>MODEL-AD_Trem2_R47H</t>
   </si>
   <si>
-    <t>UPLC-ESI-QTOF-MS</t>
+    <t>UPLC-MSMS</t>
   </si>
   <si>
     <t>MouseHAL</t>
   </si>
   <si>
-    <t>UPLC-MSMS</t>
+    <t>Vernier Caliper</t>
   </si>
   <si>
     <t>MRGWAS</t>
   </si>
   <si>
-    <t>Vernier Caliper</t>
+    <t>von Frey test</t>
   </si>
   <si>
     <t>MSBB</t>
   </si>
   <si>
-    <t>von Frey test</t>
+    <t>westernBlot</t>
   </si>
   <si>
     <t>MSBB_ArrayTissuePanel</t>
   </si>
   <si>
-    <t>westernBlot</t>
+    <t>wheel running</t>
   </si>
   <si>
     <t>MSDM</t>
   </si>
   <si>
-    <t>wheel running</t>
+    <t>whole-cell patch clamp</t>
   </si>
   <si>
     <t>MSMM</t>
   </si>
   <si>
-    <t>whole-cell patch clamp</t>
+    <t>wholeGenomeSeq</t>
   </si>
   <si>
     <t>MSSMiPSC</t>
   </si>
   <si>
-    <t>wholeGenomeSeq</t>
+    <t>Wishart Catecholamines</t>
   </si>
   <si>
     <t>mtDNA_AD</t>
   </si>
   <si>
-    <t>Wishart Catecholamines</t>
+    <t>Wishart High Value Metabolites</t>
   </si>
   <si>
     <t>NAPS</t>
   </si>
   <si>
-    <t>Wishart High Value Metabolites</t>
+    <t>Zeno Electronic Walkway</t>
   </si>
   <si>
     <t>NHP-Chimpanzee</t>
   </si>
   <si>
-    <t>Zeno Electronic Walkway</t>
-  </si>
-  <si>
     <t>NHP-Macaque</t>
   </si>
   <si>
@@ -1713,6 +1716,9 @@
     <t>TauD35</t>
   </si>
   <si>
+    <t>Test</t>
+  </si>
+  <si>
     <t>Trisomy21iN</t>
   </si>
   <si>
@@ -1777,6 +1783,9 @@
   </si>
   <si>
     <t>UPenn</t>
+  </si>
+  <si>
+    <t>Virus_Resilience_Organoids</t>
   </si>
   <si>
     <t>VirusResilience_Banner</t>
@@ -29204,32 +29213,35 @@
       <formula>$K1 = "analysis"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N1000">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$K1 = "metadata"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1000">
-    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="F1:F1000">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1000">
-    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="L1:L1000">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1000">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1000">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+  <conditionalFormatting sqref="R1:R1000">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N1000">
+    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+      <formula>$K1 = "metadata"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
+      <formula1>Sheet2!$I$2:$I$192</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
       <formula1>Sheet2!$P$2:$P$3</formula1>
     </dataValidation>
@@ -29257,9 +29269,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="L2:L1000">
       <formula1>Sheet2!$L$2:$L$24</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
-      <formula1>Sheet2!$I$2:$I$189</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$9</formula1>
     </dataValidation>
@@ -31367,6 +31376,21 @@
         <v>564</v>
       </c>
     </row>
+    <row r="190">
+      <c r="I190" s="7" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="I191" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="I192" s="7" t="s">
+        <v>567</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/current-excel-manifests/FileAnnotationTemplate.xlsx
+++ b/current-excel-manifests/FileAnnotationTemplate.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="570">
   <si>
     <t>Component</t>
   </si>
@@ -1263,349 +1263,352 @@
     <t>seg</t>
   </si>
   <si>
+    <t>Jax.IU.Pitt_B6.Klotho</t>
+  </si>
+  <si>
+    <t>open field test</t>
+  </si>
+  <si>
+    <t>Sentrix descriptor file</t>
+  </si>
+  <si>
     <t>Jax.IU.Pitt_Levetiracetam-5XFAD</t>
   </si>
   <si>
-    <t>open field test</t>
-  </si>
-  <si>
-    <t>Sentrix descriptor file</t>
+    <t>oxBS-Seq</t>
+  </si>
+  <si>
+    <t>sf3</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_LOAD2.PrimaryScreen</t>
   </si>
   <si>
-    <t>oxBS-Seq</t>
-  </si>
-  <si>
-    <t>sf3</t>
+    <t>pharmacodynamics</t>
+  </si>
+  <si>
+    <t>sif</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_MicrobiomePilot</t>
   </si>
   <si>
-    <t>pharmacodynamics</t>
-  </si>
-  <si>
-    <t>sif</t>
+    <t>pharmacokinetics</t>
+  </si>
+  <si>
+    <t>sqlite</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_PrimaryScreen</t>
   </si>
   <si>
-    <t>pharmacokinetics</t>
-  </si>
-  <si>
-    <t>sqlite</t>
+    <t>photograph</t>
+  </si>
+  <si>
+    <t>sra</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_StrainValidation</t>
   </si>
   <si>
-    <t>photograph</t>
-  </si>
-  <si>
-    <t>sra</t>
+    <t>polymeraseChainReaction</t>
+  </si>
+  <si>
+    <t>svg</t>
   </si>
   <si>
     <t>Jax.IU.Pitt_Verubecestat_5XFAD</t>
   </si>
   <si>
-    <t>polymeraseChainReaction</t>
-  </si>
-  <si>
-    <t>svg</t>
+    <t>Positron Emission Tomography</t>
+  </si>
+  <si>
+    <t>svs</t>
   </si>
   <si>
     <t>LBP</t>
   </si>
   <si>
-    <t>Positron Emission Tomography</t>
-  </si>
-  <si>
-    <t>svs</t>
+    <t>proximity extension assay</t>
+  </si>
+  <si>
+    <t>Synapse Table</t>
   </si>
   <si>
     <t>LillyMicroglia</t>
   </si>
   <si>
-    <t>proximity extension assay</t>
-  </si>
-  <si>
-    <t>Synapse Table</t>
+    <t>questionnaire</t>
+  </si>
+  <si>
+    <t>tab</t>
   </si>
   <si>
     <t>LLFS</t>
   </si>
   <si>
-    <t>questionnaire</t>
-  </si>
-  <si>
-    <t>tab</t>
+    <t>Rader Lipidomics</t>
+  </si>
+  <si>
+    <t>tagAlign</t>
   </si>
   <si>
     <t>lncRNA Pilot</t>
   </si>
   <si>
-    <t>Rader Lipidomics</t>
-  </si>
-  <si>
-    <t>tagAlign</t>
+    <t>Real Time PCR</t>
+  </si>
+  <si>
+    <t>tar</t>
   </si>
   <si>
     <t>MARS WISCONSIN</t>
   </si>
   <si>
-    <t>Real Time PCR</t>
-  </si>
-  <si>
-    <t>tar</t>
+    <t>Ribo-Seq</t>
+  </si>
+  <si>
+    <t>tbi</t>
   </si>
   <si>
     <t>MayoeGWAS</t>
   </si>
   <si>
-    <t>Ribo-Seq</t>
-  </si>
-  <si>
-    <t>tbi</t>
+    <t>rnaArray</t>
+  </si>
+  <si>
+    <t>tif</t>
   </si>
   <si>
     <t>MayoHippocampus</t>
   </si>
   <si>
-    <t>rnaArray</t>
-  </si>
-  <si>
-    <t>tif</t>
+    <t>rnaSeq</t>
+  </si>
+  <si>
+    <t>tranches</t>
   </si>
   <si>
     <t>MayoLOADGWAS</t>
   </si>
   <si>
-    <t>rnaSeq</t>
-  </si>
-  <si>
-    <t>tranches</t>
+    <t>rotarod performance test</t>
+  </si>
+  <si>
+    <t>tsv</t>
   </si>
   <si>
     <t>MayoPilotRNAseq</t>
   </si>
   <si>
-    <t>rotarod performance test</t>
-  </si>
-  <si>
-    <t>tsv</t>
+    <t>RPPA</t>
+  </si>
+  <si>
+    <t>txt</t>
   </si>
   <si>
     <t>MayoRNAseq</t>
   </si>
   <si>
-    <t>RPPA</t>
-  </si>
-  <si>
-    <t>txt</t>
+    <t>RRBS</t>
+  </si>
+  <si>
+    <t>vcf</t>
   </si>
   <si>
     <t>MC-BrAD</t>
   </si>
   <si>
-    <t>RRBS</t>
-  </si>
-  <si>
-    <t>vcf</t>
+    <t>sandwich ELISA</t>
+  </si>
+  <si>
+    <t>wiggle</t>
   </si>
   <si>
     <t>MC-CAA</t>
   </si>
   <si>
-    <t>sandwich ELISA</t>
-  </si>
-  <si>
-    <t>wiggle</t>
+    <t>Sanger sequencing</t>
+  </si>
+  <si>
+    <t>xml</t>
   </si>
   <si>
     <t>MC_snRNA</t>
   </si>
   <si>
-    <t>Sanger sequencing</t>
-  </si>
-  <si>
-    <t>xml</t>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>yaml</t>
   </si>
   <si>
     <t>mCITE-Seq</t>
   </si>
   <si>
-    <t>scale</t>
-  </si>
-  <si>
-    <t>yaml</t>
+    <t>scATACSeq</t>
+  </si>
+  <si>
+    <t>zip</t>
   </si>
   <si>
     <t>MCMPS</t>
   </si>
   <si>
-    <t>scATACSeq</t>
-  </si>
-  <si>
-    <t>zip</t>
+    <t>scCGIseq</t>
   </si>
   <si>
     <t>MEF2_Resilience</t>
   </si>
   <si>
-    <t>scCGIseq</t>
+    <t>scirnaSeq</t>
   </si>
   <si>
     <t>MindPhenomeKB</t>
   </si>
   <si>
-    <t>scirnaSeq</t>
+    <t>scrnaSeq</t>
   </si>
   <si>
     <t>miR155</t>
   </si>
   <si>
-    <t>scrnaSeq</t>
+    <t>scwholeGenomeSeq</t>
   </si>
   <si>
     <t>MIT_ROSMAP_Multiomics</t>
   </si>
   <si>
-    <t>scwholeGenomeSeq</t>
+    <t>SiMoA</t>
   </si>
   <si>
     <t>MOA-PAD</t>
   </si>
   <si>
-    <t>SiMoA</t>
+    <t>snATACSeq</t>
   </si>
   <si>
     <t>MODEL-AD_5XFAD</t>
   </si>
   <si>
-    <t>snATACSeq</t>
+    <t>snpArray</t>
   </si>
   <si>
     <t>MODEL-AD_Abca7_APOE4_Trem2</t>
   </si>
   <si>
-    <t>snpArray</t>
+    <t>snrnaSeq</t>
   </si>
   <si>
     <t>MODEL-AD_APOE4_KI</t>
   </si>
   <si>
-    <t>snrnaSeq</t>
+    <t>spontaneous alternation</t>
   </si>
   <si>
     <t>MODEL-AD_APOE4_Trem2</t>
   </si>
   <si>
-    <t>spontaneous alternation</t>
+    <t>STARRSeq</t>
   </si>
   <si>
     <t>MODEL-AD_Ceacam_KO_APOE4_Trem2</t>
   </si>
   <si>
-    <t>STARRSeq</t>
+    <t>TMT quantitation</t>
   </si>
   <si>
     <t>MODEL-AD_hAbeta_KI</t>
   </si>
   <si>
-    <t>TMT quantitation</t>
+    <t>TotalRNAseq</t>
   </si>
   <si>
     <t>MODEL-AD_Harmonization</t>
   </si>
   <si>
-    <t>TotalRNAseq</t>
+    <t>tractionForceMicroscopy</t>
   </si>
   <si>
     <t>MODEL-AD_hCR1_KI_on_APOE4_Trem2</t>
   </si>
   <si>
-    <t>tractionForceMicroscopy</t>
+    <t>UC Davis GCTOF</t>
   </si>
   <si>
     <t>MODEL-AD_hTau_Trem2</t>
   </si>
   <si>
-    <t>UC Davis GCTOF</t>
+    <t>UCSD Untargeted Metabolomics</t>
   </si>
   <si>
     <t>MODEL-AD_Il1rapKO_APOE4_Trem2_exon2KO</t>
   </si>
   <si>
-    <t>UCSD Untargeted Metabolomics</t>
+    <t>UPLC-ESI-QTOF-MS</t>
   </si>
   <si>
     <t>MODEL-AD_Mthfr_APOE4_Trem2</t>
   </si>
   <si>
-    <t>UPLC-ESI-QTOF-MS</t>
+    <t>UPLC-MSMS</t>
   </si>
   <si>
     <t>MODEL-AD_Rat_F344</t>
   </si>
   <si>
-    <t>UPLC-MSMS</t>
+    <t>Vernier Caliper</t>
   </si>
   <si>
     <t>MODEL-AD_Trem2_R47H</t>
   </si>
   <si>
-    <t>Vernier Caliper</t>
+    <t>von Frey test</t>
   </si>
   <si>
     <t>MouseHAL</t>
   </si>
   <si>
-    <t>von Frey test</t>
+    <t>westernBlot</t>
   </si>
   <si>
     <t>MRGWAS</t>
   </si>
   <si>
-    <t>westernBlot</t>
+    <t>wheel running</t>
   </si>
   <si>
     <t>MSBB</t>
   </si>
   <si>
-    <t>wheel running</t>
+    <t>whole-cell patch clamp</t>
   </si>
   <si>
     <t>MSBB_ArrayTissuePanel</t>
   </si>
   <si>
-    <t>whole-cell patch clamp</t>
+    <t>wholeGenomeSeq</t>
   </si>
   <si>
     <t>MSDM</t>
   </si>
   <si>
-    <t>wholeGenomeSeq</t>
+    <t>Wishart Catecholamines</t>
   </si>
   <si>
     <t>MSMM</t>
   </si>
   <si>
-    <t>Wishart Catecholamines</t>
+    <t>Wishart High Value Metabolites</t>
   </si>
   <si>
     <t>MSSMiPSC</t>
   </si>
   <si>
-    <t>Wishart High Value Metabolites</t>
+    <t>Zeno Electronic Walkway</t>
   </si>
   <si>
     <t>mtDNA_AD</t>
-  </si>
-  <si>
-    <t>Zeno Electronic Walkway</t>
   </si>
   <si>
     <t>NAPS</t>
@@ -29215,17 +29218,17 @@
       <formula>$M1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1000">
+  <conditionalFormatting sqref="N1:N1000">
     <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>$K1 = "experimentalData"</formula>
+      <formula>$K1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1000">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
-      <formula>$K1 = "experimentalData"</formula>
+  <conditionalFormatting sqref="O1:O1000">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+      <formula>$K1 = "analysis"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1000">
+  <conditionalFormatting sqref="L1:L1000">
     <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
@@ -29235,14 +29238,14 @@
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O1000">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
-      <formula>$K1 = "analysis"</formula>
+  <conditionalFormatting sqref="F1:F1000">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
+      <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N1000">
+  <conditionalFormatting sqref="M1:M1000">
     <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
-      <formula>$K1 = "metadata"</formula>
+      <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
@@ -29276,14 +29279,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$9</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
+      <formula1>Sheet2!$I$2:$I$194</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="K2:K1000">
       <formula1>Sheet2!$K$2:$K$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="M2:M1000">
       <formula1>Sheet2!$M$2:$M$7</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
-      <formula1>Sheet2!$I$2:$I$193</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -31403,6 +31406,11 @@
         <v>568</v>
       </c>
     </row>
+    <row r="194">
+      <c r="I194" s="7" t="s">
+        <v>569</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/current-excel-manifests/FileAnnotationTemplate.xlsx
+++ b/current-excel-manifests/FileAnnotationTemplate.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="571">
   <si>
     <t>Component</t>
   </si>
@@ -1317,295 +1317,298 @@
     <t>svg</t>
   </si>
   <si>
+    <t>Jax.IU.Pitt_TREM2.HSSvsR47H</t>
+  </si>
+  <si>
+    <t>Positron Emission Tomography</t>
+  </si>
+  <si>
+    <t>svs</t>
+  </si>
+  <si>
     <t>Jax.IU.Pitt_Verubecestat_5XFAD</t>
   </si>
   <si>
-    <t>Positron Emission Tomography</t>
-  </si>
-  <si>
-    <t>svs</t>
+    <t>proximity extension assay</t>
+  </si>
+  <si>
+    <t>Synapse Table</t>
   </si>
   <si>
     <t>LBP</t>
   </si>
   <si>
-    <t>proximity extension assay</t>
-  </si>
-  <si>
-    <t>Synapse Table</t>
+    <t>questionnaire</t>
+  </si>
+  <si>
+    <t>tab</t>
   </si>
   <si>
     <t>LillyMicroglia</t>
   </si>
   <si>
-    <t>questionnaire</t>
-  </si>
-  <si>
-    <t>tab</t>
+    <t>Rader Lipidomics</t>
+  </si>
+  <si>
+    <t>tagAlign</t>
   </si>
   <si>
     <t>LLFS</t>
   </si>
   <si>
-    <t>Rader Lipidomics</t>
-  </si>
-  <si>
-    <t>tagAlign</t>
+    <t>Real Time PCR</t>
+  </si>
+  <si>
+    <t>tar</t>
   </si>
   <si>
     <t>lncRNA Pilot</t>
   </si>
   <si>
-    <t>Real Time PCR</t>
-  </si>
-  <si>
-    <t>tar</t>
+    <t>Ribo-Seq</t>
+  </si>
+  <si>
+    <t>tbi</t>
   </si>
   <si>
     <t>MARS WISCONSIN</t>
   </si>
   <si>
-    <t>Ribo-Seq</t>
-  </si>
-  <si>
-    <t>tbi</t>
+    <t>rnaArray</t>
+  </si>
+  <si>
+    <t>tif</t>
   </si>
   <si>
     <t>MayoeGWAS</t>
   </si>
   <si>
-    <t>rnaArray</t>
-  </si>
-  <si>
-    <t>tif</t>
+    <t>rnaSeq</t>
+  </si>
+  <si>
+    <t>tranches</t>
   </si>
   <si>
     <t>MayoHippocampus</t>
   </si>
   <si>
-    <t>rnaSeq</t>
-  </si>
-  <si>
-    <t>tranches</t>
+    <t>rotarod performance test</t>
+  </si>
+  <si>
+    <t>tsv</t>
   </si>
   <si>
     <t>MayoLOADGWAS</t>
   </si>
   <si>
-    <t>rotarod performance test</t>
-  </si>
-  <si>
-    <t>tsv</t>
+    <t>RPPA</t>
+  </si>
+  <si>
+    <t>txt</t>
   </si>
   <si>
     <t>MayoPilotRNAseq</t>
   </si>
   <si>
-    <t>RPPA</t>
-  </si>
-  <si>
-    <t>txt</t>
+    <t>RRBS</t>
+  </si>
+  <si>
+    <t>vcf</t>
   </si>
   <si>
     <t>MayoRNAseq</t>
   </si>
   <si>
-    <t>RRBS</t>
-  </si>
-  <si>
-    <t>vcf</t>
+    <t>sandwich ELISA</t>
+  </si>
+  <si>
+    <t>wiggle</t>
   </si>
   <si>
     <t>MC-BrAD</t>
   </si>
   <si>
-    <t>sandwich ELISA</t>
-  </si>
-  <si>
-    <t>wiggle</t>
+    <t>Sanger sequencing</t>
+  </si>
+  <si>
+    <t>xml</t>
   </si>
   <si>
     <t>MC-CAA</t>
   </si>
   <si>
-    <t>Sanger sequencing</t>
-  </si>
-  <si>
-    <t>xml</t>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>yaml</t>
   </si>
   <si>
     <t>MC_snRNA</t>
   </si>
   <si>
-    <t>scale</t>
-  </si>
-  <si>
-    <t>yaml</t>
+    <t>scATACSeq</t>
+  </si>
+  <si>
+    <t>zip</t>
   </si>
   <si>
     <t>mCITE-Seq</t>
   </si>
   <si>
-    <t>scATACSeq</t>
-  </si>
-  <si>
-    <t>zip</t>
+    <t>scCGIseq</t>
   </si>
   <si>
     <t>MCMPS</t>
   </si>
   <si>
-    <t>scCGIseq</t>
+    <t>scirnaSeq</t>
   </si>
   <si>
     <t>MEF2_Resilience</t>
   </si>
   <si>
-    <t>scirnaSeq</t>
+    <t>scrnaSeq</t>
   </si>
   <si>
     <t>MindPhenomeKB</t>
   </si>
   <si>
-    <t>scrnaSeq</t>
+    <t>scwholeGenomeSeq</t>
   </si>
   <si>
     <t>miR155</t>
   </si>
   <si>
-    <t>scwholeGenomeSeq</t>
+    <t>SiMoA</t>
   </si>
   <si>
     <t>MIT_ROSMAP_Multiomics</t>
   </si>
   <si>
-    <t>SiMoA</t>
+    <t>snATACSeq</t>
   </si>
   <si>
     <t>MOA-PAD</t>
   </si>
   <si>
-    <t>snATACSeq</t>
+    <t>snpArray</t>
   </si>
   <si>
     <t>MODEL-AD_5XFAD</t>
   </si>
   <si>
-    <t>snpArray</t>
+    <t>snrnaSeq</t>
   </si>
   <si>
     <t>MODEL-AD_Abca7_APOE4_Trem2</t>
   </si>
   <si>
-    <t>snrnaSeq</t>
+    <t>spontaneous alternation</t>
   </si>
   <si>
     <t>MODEL-AD_APOE4_KI</t>
   </si>
   <si>
-    <t>spontaneous alternation</t>
+    <t>STARRSeq</t>
   </si>
   <si>
     <t>MODEL-AD_APOE4_Trem2</t>
   </si>
   <si>
-    <t>STARRSeq</t>
+    <t>TMT quantitation</t>
   </si>
   <si>
     <t>MODEL-AD_Ceacam_KO_APOE4_Trem2</t>
   </si>
   <si>
-    <t>TMT quantitation</t>
+    <t>TotalRNAseq</t>
   </si>
   <si>
     <t>MODEL-AD_hAbeta_KI</t>
   </si>
   <si>
-    <t>TotalRNAseq</t>
+    <t>tractionForceMicroscopy</t>
   </si>
   <si>
     <t>MODEL-AD_Harmonization</t>
   </si>
   <si>
-    <t>tractionForceMicroscopy</t>
+    <t>UC Davis GCTOF</t>
   </si>
   <si>
     <t>MODEL-AD_hCR1_KI_on_APOE4_Trem2</t>
   </si>
   <si>
-    <t>UC Davis GCTOF</t>
+    <t>UCSD Untargeted Metabolomics</t>
   </si>
   <si>
     <t>MODEL-AD_hTau_Trem2</t>
   </si>
   <si>
-    <t>UCSD Untargeted Metabolomics</t>
+    <t>UPLC-ESI-QTOF-MS</t>
   </si>
   <si>
     <t>MODEL-AD_Il1rapKO_APOE4_Trem2_exon2KO</t>
   </si>
   <si>
-    <t>UPLC-ESI-QTOF-MS</t>
+    <t>UPLC-MSMS</t>
   </si>
   <si>
     <t>MODEL-AD_Mthfr_APOE4_Trem2</t>
   </si>
   <si>
-    <t>UPLC-MSMS</t>
+    <t>Vernier Caliper</t>
   </si>
   <si>
     <t>MODEL-AD_Rat_F344</t>
   </si>
   <si>
-    <t>Vernier Caliper</t>
+    <t>von Frey test</t>
   </si>
   <si>
     <t>MODEL-AD_Trem2_R47H</t>
   </si>
   <si>
-    <t>von Frey test</t>
+    <t>westernBlot</t>
   </si>
   <si>
     <t>MouseHAL</t>
   </si>
   <si>
-    <t>westernBlot</t>
+    <t>wheel running</t>
   </si>
   <si>
     <t>MRGWAS</t>
   </si>
   <si>
-    <t>wheel running</t>
+    <t>whole-cell patch clamp</t>
   </si>
   <si>
     <t>MSBB</t>
   </si>
   <si>
-    <t>whole-cell patch clamp</t>
+    <t>wholeGenomeSeq</t>
   </si>
   <si>
     <t>MSBB_ArrayTissuePanel</t>
   </si>
   <si>
-    <t>wholeGenomeSeq</t>
+    <t>Wishart Catecholamines</t>
   </si>
   <si>
     <t>MSDM</t>
   </si>
   <si>
-    <t>Wishart Catecholamines</t>
+    <t>Wishart High Value Metabolites</t>
   </si>
   <si>
     <t>MSMM</t>
   </si>
   <si>
-    <t>Wishart High Value Metabolites</t>
+    <t>Zeno Electronic Walkway</t>
   </si>
   <si>
     <t>MSSMiPSC</t>
-  </si>
-  <si>
-    <t>Zeno Electronic Walkway</t>
   </si>
   <si>
     <t>mtDNA_AD</t>
@@ -29218,18 +29221,18 @@
       <formula>$M1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N1000">
+  <conditionalFormatting sqref="L1:L1000">
     <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>$K1 = "metadata"</formula>
+      <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O1000">
+  <conditionalFormatting sqref="M1:M1000">
     <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$K1 = "analysis"</formula>
+      <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1000">
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="F1:F1000">
+    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29238,14 +29241,14 @@
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1000">
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
-      <formula>$K1 = "experimentalData"</formula>
+  <conditionalFormatting sqref="N1:N1000">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+      <formula>$K1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1000">
+  <conditionalFormatting sqref="O1:O1000">
     <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
-      <formula>$K1 = "experimentalData"</formula>
+      <formula>$K1 = "analysis"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
@@ -29276,11 +29279,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="L2:L1000">
       <formula1>Sheet2!$L$2:$L$24</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
+      <formula1>Sheet2!$I$2:$I$195</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
-      <formula1>Sheet2!$I$2:$I$194</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="K2:K1000">
       <formula1>Sheet2!$K$2:$K$7</formula1>
@@ -31411,6 +31414,11 @@
         <v>569</v>
       </c>
     </row>
+    <row r="195">
+      <c r="I195" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/current-excel-manifests/FileAnnotationTemplate.xlsx
+++ b/current-excel-manifests/FileAnnotationTemplate.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="573">
   <si>
     <t>Component</t>
   </si>
@@ -1083,385 +1083,391 @@
     <t>lncrnaSeq</t>
   </si>
   <si>
+    <t>parquet</t>
+  </si>
+  <si>
+    <t>FreshMicro</t>
+  </si>
+  <si>
+    <t>locomotor activation behavior</t>
+  </si>
+  <si>
     <t>pdf</t>
   </si>
   <si>
-    <t>FreshMicro</t>
-  </si>
-  <si>
-    <t>locomotor activation behavior</t>
+    <t>HBI_scRNAseq</t>
+  </si>
+  <si>
+    <t>long-read rnaSeq</t>
   </si>
   <si>
     <t>pdresult</t>
   </si>
   <si>
-    <t>HBI_scRNAseq</t>
-  </si>
-  <si>
-    <t>long-read rnaSeq</t>
+    <t>HBTRC</t>
+  </si>
+  <si>
+    <t>LTP</t>
   </si>
   <si>
     <t>pdstudy</t>
   </si>
   <si>
-    <t>HBTRC</t>
-  </si>
-  <si>
-    <t>LTP</t>
+    <t>HDAC1-cKOBrain</t>
+  </si>
+  <si>
+    <t>m6A-rnaSeq</t>
   </si>
   <si>
     <t>pdview</t>
   </si>
   <si>
-    <t>HDAC1-cKOBrain</t>
-  </si>
-  <si>
-    <t>m6A-rnaSeq</t>
+    <t>HumanFC</t>
+  </si>
+  <si>
+    <t>MDMS-SL</t>
   </si>
   <si>
     <t>plink</t>
   </si>
   <si>
-    <t>HumanFC</t>
-  </si>
-  <si>
-    <t>MDMS-SL</t>
+    <t>IL10_APPmouse</t>
+  </si>
+  <si>
+    <t>memory behavior</t>
   </si>
   <si>
     <t>png</t>
   </si>
   <si>
-    <t>IL10_APPmouse</t>
-  </si>
-  <si>
-    <t>memory behavior</t>
+    <t>iNiAstshRNA</t>
+  </si>
+  <si>
+    <t>Metabolon</t>
   </si>
   <si>
     <t>powerpoint</t>
   </si>
   <si>
-    <t>iNiAstshRNA</t>
-  </si>
-  <si>
-    <t>Metabolon</t>
+    <t>IntegrativePathwayAnalysis</t>
+  </si>
+  <si>
+    <t>methylationArray</t>
   </si>
   <si>
     <t>Python script</t>
   </si>
   <si>
-    <t>IntegrativePathwayAnalysis</t>
-  </si>
-  <si>
-    <t>methylationArray</t>
+    <t>iPSC</t>
+  </si>
+  <si>
+    <t>MIB/MS</t>
   </si>
   <si>
     <t>pzfx</t>
   </si>
   <si>
-    <t>iPSC</t>
-  </si>
-  <si>
-    <t>MIB/MS</t>
+    <t>iPSC-HiC</t>
+  </si>
+  <si>
+    <t>microRNAcounts</t>
   </si>
   <si>
     <t>R script</t>
   </si>
   <si>
-    <t>iPSC-HiC</t>
-  </si>
-  <si>
-    <t>microRNAcounts</t>
-  </si>
-  <si>
     <t>iPSCAstrocytes</t>
   </si>
   <si>
     <t>mirnaArray</t>
   </si>
   <si>
+    <t>iPSCMicroglia</t>
+  </si>
+  <si>
+    <t>mirnaSeq</t>
+  </si>
+  <si>
     <t>RCC</t>
   </si>
   <si>
-    <t>iPSCMicroglia</t>
-  </si>
-  <si>
-    <t>mirnaSeq</t>
+    <t>ISB_Taner_CollagenDomain</t>
+  </si>
+  <si>
+    <t>MRI</t>
   </si>
   <si>
     <t>RData</t>
   </si>
   <si>
-    <t>ISB_Taner_CollagenDomain</t>
-  </si>
-  <si>
-    <t>MRI</t>
+    <t>ISB_Taner_Cxcl10</t>
+  </si>
+  <si>
+    <t>mRNAcounts</t>
   </si>
   <si>
     <t>recal</t>
   </si>
   <si>
-    <t>ISB_Taner_Cxcl10</t>
-  </si>
-  <si>
-    <t>mRNAcounts</t>
+    <t>ISB_Taner_PTN_MDK</t>
+  </si>
+  <si>
+    <t>mRNAseq</t>
   </si>
   <si>
     <t>RLF</t>
   </si>
   <si>
-    <t>ISB_Taner_PTN_MDK</t>
-  </si>
-  <si>
-    <t>mRNAseq</t>
+    <t>ISB_Taner_sIL10r_sIL4r</t>
+  </si>
+  <si>
+    <t>MudPIT</t>
   </si>
   <si>
     <t>rmd</t>
   </si>
   <si>
-    <t>ISB_Taner_sIL10r_sIL4r</t>
-  </si>
-  <si>
-    <t>MudPIT</t>
+    <t>ISB_Taner_TGFbeta</t>
+  </si>
+  <si>
+    <t>nextGenerationTargetedSequencing</t>
   </si>
   <si>
     <t>saf</t>
   </si>
   <si>
-    <t>ISB_Taner_TGFbeta</t>
-  </si>
-  <si>
-    <t>nextGenerationTargetedSequencing</t>
+    <t>Jax.IU.Pitt.Proteomics_Metabolomics_Pilot</t>
+  </si>
+  <si>
+    <t>Nightingale NMR</t>
   </si>
   <si>
     <t>sam</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt.Proteomics_Metabolomics_Pilot</t>
-  </si>
-  <si>
-    <t>Nightingale NMR</t>
+    <t>Jax.IU.Pitt_APOE4.Trem2.R47H</t>
+  </si>
+  <si>
+    <t>NOMe-Seq</t>
   </si>
   <si>
     <t>sav</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_APOE4.Trem2.R47H</t>
-  </si>
-  <si>
-    <t>NOMe-Seq</t>
+    <t>Jax.IU.Pitt_APP.PS1</t>
+  </si>
+  <si>
+    <t>novelty response behavior</t>
   </si>
   <si>
     <t>sdf</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_APP.PS1</t>
-  </si>
-  <si>
-    <t>novelty response behavior</t>
+    <t>Jax.IU.Pitt_B6.Klotho</t>
+  </si>
+  <si>
+    <t>open field test</t>
   </si>
   <si>
     <t>seg</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_B6.Klotho</t>
-  </si>
-  <si>
-    <t>open field test</t>
+    <t>Jax.IU.Pitt_Levetiracetam-5XFAD</t>
+  </si>
+  <si>
+    <t>oxBS-Seq</t>
   </si>
   <si>
     <t>Sentrix descriptor file</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_Levetiracetam-5XFAD</t>
-  </si>
-  <si>
-    <t>oxBS-Seq</t>
+    <t>Jax.IU.Pitt_LOAD2.PrimaryScreen</t>
+  </si>
+  <si>
+    <t>pharmacodynamics</t>
   </si>
   <si>
     <t>sf3</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_LOAD2.PrimaryScreen</t>
-  </si>
-  <si>
-    <t>pharmacodynamics</t>
+    <t>Jax.IU.Pitt_MicrobiomePilot</t>
+  </si>
+  <si>
+    <t>pharmacokinetics</t>
   </si>
   <si>
     <t>sif</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_MicrobiomePilot</t>
-  </si>
-  <si>
-    <t>pharmacokinetics</t>
+    <t>Jax.IU.Pitt_PrimaryScreen</t>
+  </si>
+  <si>
+    <t>photograph</t>
   </si>
   <si>
     <t>sqlite</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_PrimaryScreen</t>
-  </si>
-  <si>
-    <t>photograph</t>
+    <t>Jax.IU.Pitt_StrainValidation</t>
+  </si>
+  <si>
+    <t>polymeraseChainReaction</t>
   </si>
   <si>
     <t>sra</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_StrainValidation</t>
-  </si>
-  <si>
-    <t>polymeraseChainReaction</t>
+    <t>Jax.IU.Pitt_TREM2.HSSvsR47H</t>
+  </si>
+  <si>
+    <t>Positron Emission Tomography</t>
   </si>
   <si>
     <t>svg</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_TREM2.HSSvsR47H</t>
-  </si>
-  <si>
-    <t>Positron Emission Tomography</t>
+    <t>Jax.IU.Pitt_Verubecestat_5XFAD</t>
+  </si>
+  <si>
+    <t>proximity extension assay</t>
   </si>
   <si>
     <t>svs</t>
   </si>
   <si>
-    <t>Jax.IU.Pitt_Verubecestat_5XFAD</t>
-  </si>
-  <si>
-    <t>proximity extension assay</t>
+    <t>LBP</t>
+  </si>
+  <si>
+    <t>questionnaire</t>
   </si>
   <si>
     <t>Synapse Table</t>
   </si>
   <si>
-    <t>LBP</t>
-  </si>
-  <si>
-    <t>questionnaire</t>
+    <t>LillyMicroglia</t>
+  </si>
+  <si>
+    <t>Rader Lipidomics</t>
   </si>
   <si>
     <t>tab</t>
   </si>
   <si>
-    <t>LillyMicroglia</t>
-  </si>
-  <si>
-    <t>Rader Lipidomics</t>
+    <t>LLFS</t>
+  </si>
+  <si>
+    <t>Real Time PCR</t>
   </si>
   <si>
     <t>tagAlign</t>
   </si>
   <si>
-    <t>LLFS</t>
-  </si>
-  <si>
-    <t>Real Time PCR</t>
+    <t>lncRNA Pilot</t>
+  </si>
+  <si>
+    <t>Ribo-Seq</t>
   </si>
   <si>
     <t>tar</t>
   </si>
   <si>
-    <t>lncRNA Pilot</t>
-  </si>
-  <si>
-    <t>Ribo-Seq</t>
+    <t>MARS WISCONSIN</t>
+  </si>
+  <si>
+    <t>rnaArray</t>
   </si>
   <si>
     <t>tbi</t>
   </si>
   <si>
-    <t>MARS WISCONSIN</t>
-  </si>
-  <si>
-    <t>rnaArray</t>
+    <t>MayoeGWAS</t>
+  </si>
+  <si>
+    <t>rnaSeq</t>
   </si>
   <si>
     <t>tif</t>
   </si>
   <si>
-    <t>MayoeGWAS</t>
-  </si>
-  <si>
-    <t>rnaSeq</t>
+    <t>MayoHippocampus</t>
+  </si>
+  <si>
+    <t>rotarod performance test</t>
   </si>
   <si>
     <t>tranches</t>
   </si>
   <si>
-    <t>MayoHippocampus</t>
-  </si>
-  <si>
-    <t>rotarod performance test</t>
+    <t>MayoLOADGWAS</t>
+  </si>
+  <si>
+    <t>RPPA</t>
   </si>
   <si>
     <t>tsv</t>
   </si>
   <si>
-    <t>MayoLOADGWAS</t>
-  </si>
-  <si>
-    <t>RPPA</t>
+    <t>MayoPilotRNAseq</t>
+  </si>
+  <si>
+    <t>RRBS</t>
   </si>
   <si>
     <t>txt</t>
   </si>
   <si>
-    <t>MayoPilotRNAseq</t>
-  </si>
-  <si>
-    <t>RRBS</t>
+    <t>MayoRNAseq</t>
+  </si>
+  <si>
+    <t>sandwich ELISA</t>
   </si>
   <si>
     <t>vcf</t>
   </si>
   <si>
-    <t>MayoRNAseq</t>
-  </si>
-  <si>
-    <t>sandwich ELISA</t>
+    <t>MC-BrAD</t>
+  </si>
+  <si>
+    <t>Sanger sequencing</t>
   </si>
   <si>
     <t>wiggle</t>
   </si>
   <si>
-    <t>MC-BrAD</t>
-  </si>
-  <si>
-    <t>Sanger sequencing</t>
+    <t>MC-CAA</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>xenium</t>
+  </si>
+  <si>
+    <t>MC_snRNA</t>
+  </si>
+  <si>
+    <t>scATACSeq</t>
   </si>
   <si>
     <t>xml</t>
   </si>
   <si>
-    <t>MC-CAA</t>
-  </si>
-  <si>
-    <t>scale</t>
+    <t>mCITE-Seq</t>
+  </si>
+  <si>
+    <t>scCGIseq</t>
   </si>
   <si>
     <t>yaml</t>
   </si>
   <si>
-    <t>MC_snRNA</t>
-  </si>
-  <si>
-    <t>scATACSeq</t>
+    <t>MCMPS</t>
+  </si>
+  <si>
+    <t>scirnaSeq</t>
   </si>
   <si>
     <t>zip</t>
-  </si>
-  <si>
-    <t>mCITE-Seq</t>
-  </si>
-  <si>
-    <t>scCGIseq</t>
-  </si>
-  <si>
-    <t>MCMPS</t>
-  </si>
-  <si>
-    <t>scirnaSeq</t>
   </si>
   <si>
     <t>MEF2_Resilience</t>
@@ -29221,23 +29227,23 @@
       <formula>$M1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1000">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+  <conditionalFormatting sqref="R1:R1000">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>$K1 = "experimentalData"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1000">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1000">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1000">
-    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
-      <formula>$K1 = "experimentalData"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1000">
-    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="L1:L1000">
+    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29260,9 +29266,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
       <formula1>Sheet2!$H$2:$H$18</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="G2:G1000">
-      <formula1>Sheet2!$G$2:$G$97</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="Q2:Q1000">
       <formula1>Sheet2!$Q$2:$Q$26</formula1>
@@ -29291,6 +29294,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="M2:M1000">
       <formula1>Sheet2!$M$2:$M$7</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="G2:G1000">
+      <formula1>Sheet2!$G$2:$G$99</formula1>
+    </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
@@ -30504,18 +30510,18 @@
         <v>352</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>70</v>
+        <v>353</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="67">
       <c r="F67" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>355</v>
+        <v>70</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>356</v>
@@ -30855,568 +30861,574 @@
       <c r="F98" s="7" t="s">
         <v>447</v>
       </c>
+      <c r="G98" s="7" t="s">
+        <v>448</v>
+      </c>
       <c r="I98" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="99">
       <c r="F99" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>451</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="100">
       <c r="F100" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="101">
       <c r="F101" s="7" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="102">
       <c r="F102" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="103">
       <c r="F103" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="104">
       <c r="F104" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="105">
       <c r="F105" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="106">
       <c r="F106" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="107">
       <c r="F107" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="108">
       <c r="F108" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="109">
       <c r="F109" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="110">
       <c r="F110" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="111">
       <c r="F111" s="7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="112">
       <c r="F112" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="113">
       <c r="F113" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="114">
       <c r="F114" s="7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="115">
       <c r="F115" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="116">
       <c r="F116" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="117">
       <c r="F117" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="118">
       <c r="F118" s="7" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="119">
       <c r="F119" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="120">
       <c r="F120" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="121">
       <c r="F121" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="122">
       <c r="F122" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="123">
       <c r="F123" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="124">
       <c r="I124" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="125">
       <c r="I125" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="126">
       <c r="I126" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="127">
       <c r="I127" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="128">
       <c r="I128" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="129">
       <c r="I129" s="7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="130">
       <c r="I130" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="131">
       <c r="I131" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="132">
       <c r="I132" s="7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="133">
       <c r="I133" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="134">
       <c r="I134" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="135">
       <c r="I135" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="136">
       <c r="I136" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="137">
       <c r="I137" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="138">
       <c r="I138" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="139">
       <c r="I139" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="140">
       <c r="I140" s="7" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="141">
       <c r="I141" s="7" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="142">
       <c r="I142" s="7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="143">
       <c r="I143" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="144">
       <c r="I144" s="7" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="145">
       <c r="I145" s="7" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="146">
       <c r="I146" s="7" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="147">
       <c r="I147" s="7" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="148">
       <c r="I148" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="149">
       <c r="I149" s="7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="150">
       <c r="I150" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="151">
       <c r="I151" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="152">
       <c r="I152" s="7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="153">
       <c r="I153" s="7" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="154">
       <c r="I154" s="7" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="155">
       <c r="I155" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="156">
       <c r="I156" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="157">
       <c r="I157" s="7" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="158">
       <c r="I158" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="159">
       <c r="I159" s="7" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="160">
       <c r="I160" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="161">
       <c r="I161" s="7" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="162">
       <c r="I162" s="7" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="163">
       <c r="I163" s="7" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="164">
       <c r="I164" s="7" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="165">
       <c r="I165" s="7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="166">
       <c r="I166" s="7" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="167">
       <c r="I167" s="7" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="168">
       <c r="I168" s="7" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="169">
       <c r="I169" s="7" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="170">
       <c r="I170" s="7" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="171">
       <c r="I171" s="7" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="172">
       <c r="I172" s="7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="173">
       <c r="I173" s="7" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="174">
       <c r="I174" s="7" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="175">
       <c r="I175" s="7" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="176">
       <c r="I176" s="7" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="177">
       <c r="I177" s="7" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="178">
       <c r="I178" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="179">
       <c r="I179" s="7" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="180">
       <c r="I180" s="7" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="181">
       <c r="I181" s="7" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="182">
       <c r="I182" s="7" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="183">
       <c r="I183" s="7" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="184">
       <c r="I184" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="185">
       <c r="I185" s="7" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="186">
       <c r="I186" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="187">
       <c r="I187" s="7" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="188">
       <c r="I188" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="189">
       <c r="I189" s="7" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="190">
       <c r="I190" s="7" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="191">
       <c r="I191" s="7" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="192">
       <c r="I192" s="7" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="193">
       <c r="I193" s="7" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="194">
       <c r="I194" s="7" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="195">
       <c r="I195" s="7" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>

--- a/current-excel-manifests/FileAnnotationTemplate.xlsx
+++ b/current-excel-manifests/FileAnnotationTemplate.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="574">
   <si>
     <t>Component</t>
   </si>
@@ -1672,6 +1672,9 @@
   </si>
   <si>
     <t>ROSMAP_CognitiveResilience</t>
+  </si>
+  <si>
+    <t>ROSMAP_GAGE-seq</t>
   </si>
   <si>
     <t>ROSMAP_Lipidomics_Emory</t>
@@ -29227,9 +29230,9 @@
       <formula>$M1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1000">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>$K1 = "experimentalData"</formula>
+  <conditionalFormatting sqref="O1:O1000">
+    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+      <formula>$K1 = "analysis"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1000">
@@ -29237,24 +29240,24 @@
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1000">
+  <conditionalFormatting sqref="L1:L1000">
     <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1000">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="R1:R1000">
+    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
+      <formula>$K1 = "experimentalData"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:M1000">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>$K1 = "experimentalData"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1000">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
       <formula>$K1 = "metadata"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O1000">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
-      <formula>$K1 = "analysis"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
@@ -29283,7 +29286,7 @@
       <formula1>Sheet2!$L$2:$L$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
-      <formula1>Sheet2!$I$2:$I$195</formula1>
+      <formula1>Sheet2!$I$2:$I$196</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$9</formula1>
@@ -31431,6 +31434,11 @@
         <v>572</v>
       </c>
     </row>
+    <row r="196">
+      <c r="I196" s="7" t="s">
+        <v>573</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
